--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18 11:06</t>
+    <t xml:space="preserve">2026-09-06 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
